--- a/tests/sales/fixtures/sample-list.xlsx
+++ b/tests/sales/fixtures/sample-list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="240">
   <si>
     <t>orgType</t>
   </si>
@@ -574,27 +574,15 @@
     <t>Discovery</t>
   </si>
   <si>
+    <t>Jersey manager</t>
+  </si>
+  <si>
+    <t>Who handles the jerseys for [Org] — is that you, or someone else?</t>
+  </si>
+  <si>
     <t>Question</t>
   </si>
   <si>
-    <t>Who looks after jerseys for [Org] — is that you, an equipment manager, or does the board decide?</t>
-  </si>
-  <si>
-    <t>This person</t>
-  </si>
-  <si>
-    <t>Equipment manager</t>
-  </si>
-  <si>
-    <t>Board vote</t>
-  </si>
-  <si>
-    <t>Coach/manager per team</t>
-  </si>
-  <si>
-    <t>Parent committee</t>
-  </si>
-  <si>
     <t>When do you usually place your jersey order — and when's the next one?</t>
   </si>
   <si>
@@ -736,7 +724,7 @@
     <t>SCRIPT TAB — one row per line of the call, top to bottom within each Section (Opening, Discovery, Objections, Close).</t>
   </si>
   <si>
-    <t>Kind = Read: text to say. Reminder: a tick box. Question: a multiple-choice prompt (fill Option 1–6; leave all blank for a free-text answer). Objection: what they say (Text) and what you say back (Response).</t>
+    <t>Kind = Read: text to say. Reminder: a tick box. Question: a multiple-choice prompt (fill Option 1–6; leave all blank for a free-text answer). Objection: what they say (Text) and what you say back (Response). Jersey manager: asks who handles the jerseys — this person, or someone else (picked from the team's other contacts, or typed in as a new contact).</t>
   </si>
   <si>
     <t>Placeholders in Text/Response: [Name] first name (or "there"), [Full Name], [Org], [City], [Rep] (the caller), [Supplier], or any Contacts column in brackets, e.g. [Rink].</t>
@@ -2382,22 +2370,22 @@
         <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>188</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="I8" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="K8" t="s">
         <v>122</v>
@@ -2408,22 +2396,22 @@
         <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H9" t="s">
         <v>50</v>
@@ -2443,25 +2431,25 @@
         <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F10" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H10" t="s">
         <v>197</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H10" t="s">
-        <v>201</v>
       </c>
       <c r="I10" t="s">
         <v>122</v>
@@ -2478,28 +2466,28 @@
         <v>185</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G11" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" t="s">
         <v>202</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="I11" t="s">
         <v>203</v>
-      </c>
-      <c r="F11" t="s">
-        <v>204</v>
-      </c>
-      <c r="G11" t="s">
-        <v>205</v>
-      </c>
-      <c r="H11" t="s">
-        <v>206</v>
-      </c>
-      <c r="I11" t="s">
-        <v>207</v>
       </c>
       <c r="J11" t="s">
         <v>122</v>
@@ -2513,10 +2501,10 @@
         <v>185</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>122</v>
@@ -2548,25 +2536,25 @@
         <v>185</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" t="s">
+        <v>207</v>
+      </c>
+      <c r="G13" t="s">
+        <v>208</v>
+      </c>
+      <c r="H13" t="s">
         <v>209</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" t="s">
-        <v>210</v>
-      </c>
-      <c r="F13" t="s">
-        <v>211</v>
-      </c>
-      <c r="G13" t="s">
-        <v>212</v>
-      </c>
-      <c r="H13" t="s">
-        <v>213</v>
       </c>
       <c r="I13" t="s">
         <v>42</v>
@@ -2580,16 +2568,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B14" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -2615,16 +2603,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" s="4" t="s">
         <v>215</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="E15" t="s">
         <v>122</v>
@@ -2650,16 +2638,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E16" t="s">
         <v>122</v>
@@ -2685,16 +2673,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -2720,16 +2708,16 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
         <v>122</v>
@@ -2755,13 +2743,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s">
         <v>177</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>122</v>
@@ -2790,13 +2778,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s">
         <v>175</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>122</v>
@@ -2825,13 +2813,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B21" t="s">
         <v>175</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>122</v>
@@ -2864,7 +2852,7 @@
       <formula1>"Opening,Discovery,Objections,Close"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B2000">
-      <formula1>"Read,Reminder,Question,Objection"</formula1>
+      <formula1>"Read,Reminder,Question,Objection,Jersey manager"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2882,7 +2870,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2892,42 +2880,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2937,22 +2925,22 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -2962,7 +2950,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/tests/sales/fixtures/sample-list.xlsx
+++ b/tests/sales/fixtures/sample-list.xlsx
@@ -733,7 +733,7 @@
     <t>Show When: leave blank to always show. Otherwise a rule like  Org Type = Minor Hockey Association  or  Role != Head Coach  — several values with commas (any of), several rules with semicolons (all of).</t>
   </si>
   <si>
-    <t>UPLOADING — save this file and upload it on the Sales page. Each upload makes a new list; re-upload to change the script or add people. Results come back out with Export CSV.</t>
+    <t>UPLOADING — save this file and upload it into a list on the Sales page, as often as you like. A row with the same phone or email as a contact already in the list fills in that contact's blanks instead of being added twice. The Script tab is optional once the list has a script; include it to replace the script. Results come back out with Export CSV.</t>
   </si>
 </sst>
 </file>

--- a/tests/sales/fixtures/sample-list.xlsx
+++ b/tests/sales/fixtures/sample-list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="220">
   <si>
     <t>orgType</t>
   </si>
@@ -583,67 +583,7 @@
     <t>Question</t>
   </si>
   <si>
-    <t>When do you usually place your jersey order — and when's the next one?</t>
-  </si>
-  <si>
-    <t>This season</t>
-  </si>
-  <si>
-    <t>Next season</t>
-  </si>
-  <si>
-    <t>No plan yet</t>
-  </si>
-  <si>
-    <t>Who are you using today, and how's that going?</t>
-  </si>
-  <si>
-    <t>Happy</t>
-  </si>
-  <si>
-    <t>Fine</t>
-  </si>
-  <si>
-    <t>Unhappy</t>
-  </si>
-  <si>
-    <t>No supplier</t>
-  </si>
-  <si>
-    <t>What's in a typical order — jerseys only, socks, pant shells? One set or home and away?</t>
-  </si>
-  <si>
-    <t>Jerseys only</t>
-  </si>
-  <si>
-    <t>Jerseys + socks</t>
-  </si>
-  <si>
-    <t>Jerseys + socks + pants</t>
-  </si>
-  <si>
-    <t>Home &amp; away sets</t>
-  </si>
-  <si>
-    <t>Association-wide</t>
-  </si>
-  <si>
     <t>Roughly how many teams and players are we talking?</t>
-  </si>
-  <si>
-    <t>When you pick a supplier, what matters most?</t>
-  </si>
-  <si>
-    <t>Turnaround</t>
-  </si>
-  <si>
-    <t>Durability</t>
-  </si>
-  <si>
-    <t>Design help</t>
-  </si>
-  <si>
-    <t>Low minimums</t>
   </si>
   <si>
     <t>Objections</t>
@@ -2103,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -2405,16 +2345,16 @@
         <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
-        <v>191</v>
+        <v>122</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
         <v>122</v>
@@ -2428,28 +2368,28 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="E10" t="s">
-        <v>194</v>
+        <v>122</v>
       </c>
       <c r="F10" t="s">
-        <v>195</v>
+        <v>122</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="H10" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="I10" t="s">
         <v>122</v>
@@ -2463,31 +2403,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="F11" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>201</v>
+        <v>122</v>
       </c>
       <c r="H11" t="s">
-        <v>202</v>
+        <v>122</v>
       </c>
       <c r="I11" t="s">
-        <v>203</v>
+        <v>122</v>
       </c>
       <c r="J11" t="s">
         <v>122</v>
@@ -2498,16 +2438,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="E12" t="s">
         <v>122</v>
@@ -2533,34 +2473,34 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="E13" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>122</v>
       </c>
       <c r="H13" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="I13" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="K13" t="s">
         <v>122</v>
@@ -2568,16 +2508,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -2603,16 +2543,16 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
         <v>122</v>
@@ -2638,16 +2578,16 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>217</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>122</v>
@@ -2673,16 +2613,16 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
         <v>122</v>
@@ -2703,146 +2643,6 @@
         <v>122</v>
       </c>
       <c r="K17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E18" t="s">
-        <v>122</v>
-      </c>
-      <c r="F18" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" t="s">
-        <v>122</v>
-      </c>
-      <c r="J18" t="s">
-        <v>122</v>
-      </c>
-      <c r="K18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" t="s">
-        <v>122</v>
-      </c>
-      <c r="G19" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" t="s">
-        <v>122</v>
-      </c>
-      <c r="J19" t="s">
-        <v>122</v>
-      </c>
-      <c r="K19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" t="s">
-        <v>122</v>
-      </c>
-      <c r="G20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" t="s">
-        <v>122</v>
-      </c>
-      <c r="I20" t="s">
-        <v>122</v>
-      </c>
-      <c r="J20" t="s">
-        <v>122</v>
-      </c>
-      <c r="K20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B21" t="s">
-        <v>175</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>122</v>
-      </c>
-      <c r="F21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" t="s">
-        <v>122</v>
-      </c>
-      <c r="J21" t="s">
-        <v>122</v>
-      </c>
-      <c r="K21" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2870,7 +2670,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2880,42 +2680,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2925,22 +2725,22 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -2950,7 +2750,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/tests/sales/fixtures/sample-list.xlsx
+++ b/tests/sales/fixtures/sample-list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="218">
   <si>
     <t>orgType</t>
   </si>
@@ -578,12 +578,6 @@
   </si>
   <si>
     <t>Who handles the jerseys for [Org] — is that you, or someone else?</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>Roughly how many teams and players are we talking?</t>
   </si>
   <si>
     <t>Objections</t>
@@ -2043,7 +2037,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -2333,16 +2327,16 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="E9" t="s">
         <v>122</v>
@@ -2368,10 +2362,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>192</v>
@@ -2403,10 +2397,10 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>194</v>
@@ -2438,10 +2432,10 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>196</v>
@@ -2473,10 +2467,10 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>198</v>
@@ -2508,16 +2502,16 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="B14" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>201</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -2543,13 +2537,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>200</v>
+      </c>
+      <c r="B15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="B15" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>122</v>
@@ -2578,13 +2572,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s">
         <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>122</v>
@@ -2608,41 +2602,6 @@
         <v>122</v>
       </c>
       <c r="K16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>202</v>
-      </c>
-      <c r="B17" t="s">
-        <v>175</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E17" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" t="s">
-        <v>122</v>
-      </c>
-      <c r="K17" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2670,7 +2629,7 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2680,42 +2639,42 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -2725,22 +2684,22 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
@@ -2750,7 +2709,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
